--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU12/HRM/post FET_HRM-2031-0300/Panel 7/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU12_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU12/HRM/post FET_HRM-2031-0300/Panel 7/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU12_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.86878</v>
+        <v>17.73702</v>
       </c>
       <c r="D2" t="n">
-        <v>17.7827</v>
+        <v>17.62495</v>
       </c>
       <c r="E2" t="n">
-        <v>17.28397</v>
+        <v>17.65233</v>
       </c>
       <c r="F2" t="n">
-        <v>45.63787</v>
+        <v>44.71879</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0529</v>
+        <v>0.05352</v>
       </c>
       <c r="H2" t="n">
-        <v>1.94975</v>
+        <v>1.89392</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.8361</v>
+        <v>17.85959</v>
       </c>
       <c r="D3" t="n">
-        <v>17.91583</v>
+        <v>17.59255</v>
       </c>
       <c r="E3" t="n">
-        <v>17.75743</v>
+        <v>17.65315</v>
       </c>
       <c r="F3" t="n">
-        <v>44.91044</v>
+        <v>45.2493</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05308</v>
+        <v>0.05494</v>
       </c>
       <c r="H3" t="n">
-        <v>1.90248</v>
+        <v>1.94606</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18.08628</v>
+        <v>17.62728</v>
       </c>
       <c r="D4" t="n">
-        <v>17.41323</v>
+        <v>17.22995</v>
       </c>
       <c r="E4" t="n">
-        <v>17.7588</v>
+        <v>17.44359</v>
       </c>
       <c r="F4" t="n">
-        <v>45.94111</v>
+        <v>45.71295</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05382</v>
+        <v>0.05357</v>
       </c>
       <c r="H4" t="n">
-        <v>1.94181</v>
+        <v>1.92575</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18.0236</v>
+        <v>17.54263</v>
       </c>
       <c r="D6" t="n">
-        <v>16.83503</v>
+        <v>16.79948</v>
       </c>
       <c r="E6" t="n">
-        <v>17.45062</v>
+        <v>17.35289</v>
       </c>
       <c r="F6" t="n">
-        <v>23.12445</v>
+        <v>23.09292</v>
       </c>
       <c r="G6" t="n">
-        <v>36.52587</v>
+        <v>36.80272</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.89405</v>
+        <v>17.88504</v>
       </c>
       <c r="D7" t="n">
-        <v>16.84262</v>
+        <v>16.86429</v>
       </c>
       <c r="E7" t="n">
-        <v>17.01389</v>
+        <v>17.64377</v>
       </c>
       <c r="F7" t="n">
-        <v>23.08317</v>
+        <v>23.12605</v>
       </c>
       <c r="G7" t="n">
-        <v>35.93953</v>
+        <v>35.5735</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.9698</v>
+        <v>18.05581</v>
       </c>
       <c r="D8" t="n">
-        <v>16.52845</v>
+        <v>16.92858</v>
       </c>
       <c r="E8" t="n">
-        <v>17.23842</v>
+        <v>17.18842</v>
       </c>
       <c r="F8" t="n">
-        <v>23.14112</v>
+        <v>23.21531</v>
       </c>
       <c r="G8" t="n">
-        <v>35.99846</v>
+        <v>35.8443</v>
       </c>
     </row>
   </sheetData>
